--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484291_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484291_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4634</v>
+        <v>6.3933</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8809</v>
+        <v>6.0831</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5826</v>
+        <v>0.3102</v>
       </c>
       <c r="G2" t="n">
         <v>5.6066</v>
@@ -610,13 +610,13 @@
         <v>1.1721</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0522</v>
+        <v>-0.0179</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1457</v>
+        <v>0.0566</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1978</v>
+        <v>-0.0745</v>
       </c>
       <c r="V2" t="n">
         <v>0.6093</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. SALMERON SEGU</t>
+          <t>O. TOURE JABBY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4336</v>
+        <v>0.0247</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6927</v>
+        <v>1.5234</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.2591</v>
+        <v>-1.4988</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.8455</v>
+        <v>-0.7836</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2827</v>
+        <v>0.3901</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.5628</v>
+        <v>-1.1737</v>
       </c>
       <c r="J3" t="n">
-        <v>0.211</v>
+        <v>0.9243</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8851</v>
+        <v>1.5579</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6741</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.0565</v>
+        <v>-1.7079</v>
       </c>
       <c r="N3" t="n">
         <v>-1.1678</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.8887</v>
+        <v>-0.5401</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9702</v>
+        <v>-0.5276</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2631</v>
+        <v>-0.5646</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2928</v>
+        <v>0.037</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9414</v>
+        <v>0.5545</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2186</v>
+        <v>1.1638</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2772</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. TOURE JABBY</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1142</v>
+        <v>-0.0511</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4223</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3081</v>
+        <v>0.4625</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.7836</v>
+        <v>-1.1066</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3901</v>
+        <v>-1.133</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.1737</v>
+        <v>0.0265</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9243</v>
+        <v>-0.328</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5579</v>
+        <v>0.1842</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-0.5122</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7079</v>
+        <v>-0.7785</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1678</v>
+        <v>-1.3172</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5401</v>
+        <v>0.5387</v>
       </c>
       <c r="P4" t="n">
         <v>0.7814</v>
@@ -766,28 +766,28 @@
         <v>0.7814</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4381</v>
+        <v>-0.1128</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6657</v>
+        <v>-0.1855</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2277</v>
+        <v>0.0727</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5545</v>
+        <v>0.3869</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1638</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6093</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>M. SALMERON SEGU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2866</v>
+        <v>-0.3887</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7763</v>
+        <v>1.8432</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4898</v>
+        <v>-2.2319</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.1066</v>
+        <v>-2.8455</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.133</v>
+        <v>-0.2827</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0265</v>
+        <v>-2.5628</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.328</v>
+        <v>0.211</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1842</v>
+        <v>0.8851</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5122</v>
+        <v>-0.6741</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7785</v>
+        <v>-3.0565</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3172</v>
+        <v>-1.1678</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5387</v>
+        <v>-1.8887</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3483</v>
+        <v>0.148</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4483</v>
+        <v>0.4135</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1</v>
+        <v>-0.2656</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3869</v>
+        <v>0.9414</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3869</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.5097</v>
+        <v>-1.4825</v>
       </c>
       <c r="E6" t="n">
         <v>-0.2208</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2889</v>
+        <v>-1.2617</v>
       </c>
       <c r="G6" t="n">
         <v>-1.6159</v>
@@ -922,13 +922,13 @@
         <v>0.3907</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2845</v>
+        <v>-0.2572</v>
       </c>
       <c r="T6" t="n">
         <v>-0.3026</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. JUAREZ GIMENEZ</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.5515</v>
+        <v>-2.1798</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.8156</v>
+        <v>-0.5723</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2641</v>
+        <v>-1.6074</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.9581</v>
+        <v>-1.4143</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.1873</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2292</v>
+        <v>-0.4319</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.2729</v>
+        <v>-0.2505</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.6936</v>
+        <v>-0.2239</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5794</v>
+        <v>-0.0266</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3148</v>
+        <v>-1.1638</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4937</v>
+        <v>-0.7585</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8085</v>
+        <v>-0.4052</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.9534</v>
+        <v>0.3907</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1359</v>
+        <v>-0.2696</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8915999999999999</v>
+        <v>-0.3218</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0274</v>
+        <v>0.0522</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4959</v>
+        <v>-0.8865</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>J. JUAREZ GIMENEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.911</v>
+        <v>-2.8992</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9768</v>
+        <v>-3.4629</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.9343</v>
+        <v>0.5637</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4143</v>
+        <v>-1.9581</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9824000000000001</v>
+        <v>-2.1873</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4319</v>
+        <v>0.2292</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2505</v>
+        <v>-2.2729</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2239</v>
+        <v>-1.6936</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0266</v>
+        <v>-0.5794</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1638</v>
+        <v>0.3148</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7585</v>
+        <v>-0.4937</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4052</v>
+        <v>0.8085</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3907</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q8" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.4836</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.2443</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.7278</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.4959</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.4959</v>
+      </c>
+      <c r="X8" t="n">
         <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.3907</v>
-      </c>
-      <c r="S8" t="n">
-        <v>-1.0009</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-0.7262999999999999</v>
-      </c>
-      <c r="U8" t="n">
-        <v>-0.2746</v>
-      </c>
-      <c r="V8" t="n">
-        <v>-0.8865</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-0.8865</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. PRAT PRUNA</t>
+          <t>A. PEIRO COSMO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.7226</v>
+        <v>-3.3555</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.698</v>
+        <v>-3.582</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0246</v>
+        <v>0.2265</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.2101</v>
+        <v>-2.2594</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.6035</v>
+        <v>-1.14</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6066</v>
+        <v>-1.1194</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.2589</v>
+        <v>-1.9647</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.3047</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.9542</v>
+        <v>-1.2535</v>
       </c>
       <c r="M9" t="n">
-        <v>1.0488</v>
+        <v>-0.2947</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2988</v>
+        <v>-0.4287</v>
       </c>
       <c r="O9" t="n">
-        <v>1.3476</v>
+        <v>0.134</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.7348</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6129</v>
+        <v>-0.5138</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4212</v>
+        <v>-0.2537</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1918</v>
+        <v>-0.2601</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6093</v>
+        <v>-0.3869</v>
       </c>
       <c r="W9" t="n">
-        <v>3.0466</v>
+        <v>-0.3869</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.921</v>
+        <v>-3.6388</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.236</v>
+        <v>-1.8721</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.685</v>
+        <v>-1.7667</v>
       </c>
       <c r="G10" t="n">
         <v>-2.5482</v>
@@ -1234,13 +1234,13 @@
         <v>1.1721</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6267</v>
+        <v>-0.3446</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6987</v>
+        <v>-0.3349</v>
       </c>
       <c r="U10" t="n">
-        <v>0.07199999999999999</v>
+        <v>-0.0097</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9414</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. PEIRO COSMO</t>
+          <t>G. PRAT PRUNA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9972</v>
+        <v>-4.2572</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0876</v>
+        <v>-4.042</v>
       </c>
       <c r="F11" t="n">
-        <v>0.09030000000000001</v>
+        <v>-0.2152</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.2594</v>
+        <v>-2.2101</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.14</v>
+        <v>-1.6035</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1194</v>
+        <v>-0.6066</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.9647</v>
+        <v>-3.2589</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7112000000000001</v>
+        <v>-1.3047</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2535</v>
+        <v>-1.9542</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2947</v>
+        <v>1.0488</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4287</v>
+        <v>-0.2988</v>
       </c>
       <c r="O11" t="n">
-        <v>0.134</v>
+        <v>1.3476</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1953</v>
+        <v>-2.7348</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1556</v>
+        <v>0.0784</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7592</v>
+        <v>0.0772</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3963</v>
+        <v>0.0011</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3869</v>
+        <v>0.6093</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3869</v>
+        <v>3.0466</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.5186</v>
+        <v>-4.2698</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6844</v>
+        <v>-2.381</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8343</v>
+        <v>-1.8887</v>
       </c>
       <c r="G12" t="n">
         <v>-3.7477</v>
@@ -1390,13 +1390,13 @@
         <v>0.7814</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5756</v>
+        <v>-0.3267</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0289</v>
+        <v>-0.7255</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4533</v>
+        <v>0.3988</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-16.407</v>
+        <v>-16.1046</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.499600000000001</v>
+        <v>-7.197000000000001</v>
       </c>
       <c r="F13" t="n">
         <v>-8.907500000000001</v>
@@ -1438,13 +1438,13 @@
         <v>-9.4861</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.396699999999999</v>
+        <v>-5.396700000000001</v>
       </c>
       <c r="J13" t="n">
         <v>-2.148</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.1308</v>
+        <v>-0.1307999999999998</v>
       </c>
       <c r="L13" t="n">
         <v>-2.017300000000001</v>
@@ -1456,25 +1456,25 @@
         <v>-9.3552</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.379500000000001</v>
+        <v>-3.3795</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9766000000000004</v>
+        <v>-0.9765999999999995</v>
       </c>
       <c r="Q13" t="n">
         <v>-10.7438</v>
       </c>
       <c r="R13" t="n">
-        <v>9.767399999999999</v>
+        <v>9.7674</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.9303</v>
+        <v>-2.627400000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.1995</v>
+        <v>-1.897</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7303000000000002</v>
+        <v>-0.7304999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>2.3825</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.4301</v>
+        <v>6.848</v>
       </c>
       <c r="E14" t="n">
-        <v>3.608</v>
+        <v>3.0013</v>
       </c>
       <c r="F14" t="n">
-        <v>3.8221</v>
+        <v>3.8466</v>
       </c>
       <c r="G14" t="n">
         <v>3.6733</v>
@@ -1546,13 +1546,13 @@
         <v>1.5627</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0926</v>
+        <v>1.5105</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2217</v>
+        <v>0.615</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8709</v>
+        <v>0.8954</v>
       </c>
       <c r="V14" t="n">
         <v>1.2735</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.5175</v>
+        <v>5.9021</v>
       </c>
       <c r="E15" t="n">
-        <v>5.653</v>
+        <v>6.3608</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1355</v>
+        <v>-0.4587</v>
       </c>
       <c r="G15" t="n">
         <v>5.1194</v>
@@ -1624,13 +1624,13 @@
         <v>2.1488</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2931</v>
+        <v>0.0915</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.96</v>
+        <v>-0.2522</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3331</v>
+        <v>0.3437</v>
       </c>
       <c r="V15" t="n">
         <v>0.8865</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4218</v>
+        <v>3.4879</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4429</v>
+        <v>1.6451</v>
       </c>
       <c r="F16" t="n">
-        <v>1.979</v>
+        <v>1.8428</v>
       </c>
       <c r="G16" t="n">
         <v>3.4876</v>
@@ -1702,13 +1702,13 @@
         <v>0.7814</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4264</v>
+        <v>0.4924</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4566</v>
+        <v>-0.2544</v>
       </c>
       <c r="U16" t="n">
-        <v>0.883</v>
+        <v>0.7468</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2735</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2832</v>
+        <v>1.3926</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2177</v>
+        <v>1.0044</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0655</v>
+        <v>0.3882</v>
       </c>
       <c r="G17" t="n">
         <v>1.0669</v>
@@ -1780,13 +1780,13 @@
         <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>2.1494</v>
+        <v>1.2588</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9785</v>
+        <v>0.7651</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1709</v>
+        <v>0.4937</v>
       </c>
       <c r="V17" t="n">
         <v>-2.1052</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0752</v>
+        <v>1.1297</v>
       </c>
       <c r="E18" t="n">
         <v>0.5739</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5013</v>
+        <v>0.5558</v>
       </c>
       <c r="G18" t="n">
         <v>0.9041</v>
@@ -1858,13 +1858,13 @@
         <v>0.1953</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0242</v>
+        <v>0.0303</v>
       </c>
       <c r="T18" t="n">
         <v>-0.0605</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0363</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. LLUFRIU ARCOS</t>
+          <t>M. CORBERA BUSQUETA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4047</v>
+        <v>0.6407</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6848</v>
+        <v>-1.8573</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2801</v>
+        <v>2.498</v>
       </c>
       <c r="G19" t="n">
-        <v>2.1043</v>
+        <v>0.5958</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0243</v>
+        <v>0.1108</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0799</v>
+        <v>0.485</v>
       </c>
       <c r="J19" t="n">
-        <v>2.5338</v>
+        <v>-0.0436</v>
       </c>
       <c r="K19" t="n">
-        <v>0.779</v>
+        <v>-0.2597</v>
       </c>
       <c r="L19" t="n">
-        <v>1.7548</v>
+        <v>0.2161</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4295</v>
+        <v>0.6393</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2454</v>
+        <v>0.3705</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6749000000000001</v>
+        <v>0.2688</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3907</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1953</v>
+        <v>-3.3208</v>
       </c>
       <c r="R19" t="n">
-        <v>0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2074</v>
+        <v>0.0337</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2667</v>
+        <v>-0.266</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0593</v>
+        <v>0.2997</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8828</v>
+        <v>2.16</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3869</v>
+        <v>1.7731</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.4959</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. ANDUJAR MASCARO</t>
+          <t>S. LLUFRIU ARCOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2221</v>
+        <v>0.4306</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4732</v>
+        <v>1.6848</v>
       </c>
       <c r="F20" t="n">
-        <v>0.251</v>
+        <v>-1.2542</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0172</v>
+        <v>2.1043</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0691</v>
+        <v>1.0243</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0519</v>
+        <v>1.0799</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2723</v>
+        <v>2.5338</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5104</v>
+        <v>0.779</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7827</v>
+        <v>1.7548</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2895</v>
+        <v>-0.4295</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5587</v>
+        <v>0.2454</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2692</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P20" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="R20" t="n">
         <v>0.586</v>
       </c>
-      <c r="Q20" t="n">
-        <v>-0.9767</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.5627</v>
-      </c>
       <c r="S20" t="n">
-        <v>0.4276</v>
+        <v>-0.1816</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2312</v>
+        <v>-0.2667</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1964</v>
+        <v>0.0851</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2186</v>
+        <v>-1.8828</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.3869</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. CORBERA BUSQUETA</t>
+          <t>L. ANDUJAR MASCARO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7984</v>
+        <v>0.023</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5651</v>
+        <v>-0.4732</v>
       </c>
       <c r="F21" t="n">
-        <v>1.7667</v>
+        <v>0.4962</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5958</v>
+        <v>-0.0172</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1108</v>
+        <v>-1.0691</v>
       </c>
       <c r="I21" t="n">
-        <v>0.485</v>
+        <v>1.0519</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0436</v>
+        <v>0.2723</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2597</v>
+        <v>-0.5104</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2161</v>
+        <v>0.7827</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6393</v>
+        <v>-0.2895</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3705</v>
+        <v>-0.5587</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2688</v>
+        <v>0.2692</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.1488</v>
+        <v>0.586</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.3208</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4054</v>
+        <v>0.6727</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9738</v>
+        <v>0.2312</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4316</v>
+        <v>0.4415</v>
       </c>
       <c r="V21" t="n">
-        <v>2.16</v>
+        <v>-1.2186</v>
       </c>
       <c r="W21" t="n">
-        <v>1.7731</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3869</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.705</v>
+        <v>-1.4251</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2345</v>
+        <v>-3.0323</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5296</v>
+        <v>1.6072</v>
       </c>
       <c r="G22" t="n">
         <v>-2.0515</v>
@@ -2170,13 +2170,13 @@
         <v>1.1721</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7643</v>
+        <v>1.0441</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0167</v>
+        <v>0.2189</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7476</v>
+        <v>0.8252</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2224</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>16.407</v>
+        <v>18.4295</v>
       </c>
       <c r="E23" t="n">
-        <v>8.907499999999997</v>
+        <v>8.907499999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>7.4996</v>
+        <v>9.5219</v>
       </c>
       <c r="G23" t="n">
         <v>14.8827</v>
@@ -2239,7 +2239,7 @@
         <v>2.0173</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9767999999999994</v>
+        <v>0.9767999999999997</v>
       </c>
       <c r="Q23" t="n">
         <v>-9.767099999999999</v>
@@ -2248,13 +2248,13 @@
         <v>10.7438</v>
       </c>
       <c r="S23" t="n">
-        <v>2.9302</v>
+        <v>4.9524</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7305</v>
+        <v>0.7303999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>2.1997</v>
+        <v>4.2219</v>
       </c>
       <c r="V23" t="n">
         <v>-2.3825</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484291_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484291_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,11 +632,16 @@
       <c r="X2" t="n">
         <v>-0.8317</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484291_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O. TOURE JABBY</t>
+          <t>A. VIÑALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +653,78 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0247</v>
+        <v>0.307</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5234</v>
+        <v>0.307</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.4988</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.7836</v>
+        <v>0.307</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3901</v>
+        <v>0.307</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.1737</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9243</v>
+        <v>0.307</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5579</v>
+        <v>0.307</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.7079</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1678</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5401</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5276</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5646</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.037</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1638</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484291_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>O. TOURE JABBY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +736,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0511</v>
+        <v>0.0247</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5135999999999999</v>
+        <v>1.5234</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4625</v>
+        <v>-1.4988</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.1066</v>
+        <v>-0.7836</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.133</v>
+        <v>0.3901</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0265</v>
+        <v>-1.1737</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.328</v>
+        <v>0.9243</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1842</v>
+        <v>1.5579</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5122</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7785</v>
+        <v>-1.7079</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3172</v>
+        <v>-1.1678</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5387</v>
+        <v>-0.5401</v>
       </c>
       <c r="P4" t="n">
         <v>0.7814</v>
@@ -766,28 +781,33 @@
         <v>0.7814</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1128</v>
+        <v>-0.5276</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1855</v>
+        <v>-0.5646</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0727</v>
+        <v>0.037</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3869</v>
+        <v>0.5545</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.1638</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3869</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484291_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. SALMERON SEGU</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3887</v>
+        <v>-0.0511</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8432</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.2319</v>
+        <v>0.4625</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.8455</v>
+        <v>-1.1066</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2827</v>
+        <v>-1.133</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.5628</v>
+        <v>0.0265</v>
       </c>
       <c r="J5" t="n">
-        <v>0.211</v>
+        <v>-0.328</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8851</v>
+        <v>0.1842</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6741</v>
+        <v>-0.5122</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.0565</v>
+        <v>-0.7785</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1678</v>
+        <v>-1.3172</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.8887</v>
+        <v>0.5387</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="S5" t="n">
-        <v>0.148</v>
+        <v>-0.1128</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4135</v>
+        <v>-0.1855</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2656</v>
+        <v>0.0727</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9414</v>
+        <v>0.3869</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2772</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484291_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MARTÍN ADELANTADO</t>
+          <t>M. SALMERON SEGU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.4825</v>
+        <v>-0.3887</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2208</v>
+        <v>1.8432</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2617</v>
+        <v>-2.2319</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.6159</v>
+        <v>-2.8455</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8066</v>
+        <v>-0.2827</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8093</v>
+        <v>-2.5628</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0819</v>
+        <v>0.211</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0819</v>
+        <v>0.8851</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.6741</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6978</v>
+        <v>-3.0565</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8885</v>
+        <v>-1.1678</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8093</v>
+        <v>-1.8887</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3907</v>
+        <v>1.3674</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3907</v>
+        <v>1.3674</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2572</v>
+        <v>0.148</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3026</v>
+        <v>0.4135</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0454</v>
+        <v>-0.2656</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.9414</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484291_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>A. MARTIN ADELANTADO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +985,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1798</v>
+        <v>-1.4825</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5723</v>
+        <v>-0.2208</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6074</v>
+        <v>-1.2617</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4143</v>
+        <v>-1.6159</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9824000000000001</v>
+        <v>-0.8066</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4319</v>
+        <v>-0.8093</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2505</v>
+        <v>0.0819</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2239</v>
+        <v>0.0819</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0266</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1638</v>
+        <v>-1.6978</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7585</v>
+        <v>-0.8885</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4052</v>
+        <v>-0.8093</v>
       </c>
       <c r="P7" t="n">
         <v>0.3907</v>
@@ -1000,28 +1030,33 @@
         <v>0.3907</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2696</v>
+        <v>-0.2572</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3218</v>
+        <v>-0.3026</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0522</v>
+        <v>0.0454</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484291_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. JUAREZ GIMENEZ</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.8992</v>
+        <v>-2.1798</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.4629</v>
+        <v>-0.5723</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5637</v>
+        <v>-1.6074</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.9581</v>
+        <v>-1.4143</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.1873</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2292</v>
+        <v>-0.4319</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.2729</v>
+        <v>-0.2505</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.6936</v>
+        <v>-0.2239</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5794</v>
+        <v>-0.0266</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3148</v>
+        <v>-1.1638</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4937</v>
+        <v>-0.7585</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8085</v>
+        <v>-0.4052</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.9534</v>
+        <v>0.3907</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4836</v>
+        <v>-0.2696</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2443</v>
+        <v>-0.3218</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7278</v>
+        <v>0.0522</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4959</v>
+        <v>-0.8865</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484291_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. PEIRO COSMO</t>
+          <t>J. JUAREZ GIMENEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3555</v>
+        <v>-2.8992</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.582</v>
+        <v>-3.4629</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2265</v>
+        <v>0.5637</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.2594</v>
+        <v>-1.9581</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.14</v>
+        <v>-2.1873</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1194</v>
+        <v>0.2292</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.9647</v>
+        <v>-2.2729</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7112000000000001</v>
+        <v>-1.6936</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2535</v>
+        <v>-0.5794</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2947</v>
+        <v>0.3148</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4287</v>
+        <v>-0.4937</v>
       </c>
       <c r="O9" t="n">
-        <v>0.134</v>
+        <v>0.8085</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1953</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5138</v>
+        <v>-0.4836</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2537</v>
+        <v>0.2443</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2601</v>
+        <v>-0.7278</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3869</v>
+        <v>1.4959</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3869</v>
+        <v>1.4959</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484291_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. TORNÉ DELAURENS</t>
+          <t>A. PEIRO COSMO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6388</v>
+        <v>-3.3555</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8721</v>
+        <v>-3.582</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7667</v>
+        <v>0.2265</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.5482</v>
+        <v>-2.2594</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.3339</v>
+        <v>-1.14</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2144</v>
+        <v>-1.1194</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1036</v>
+        <v>-1.9647</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1036</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-1.2535</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.6518</v>
+        <v>-0.2947</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4375</v>
+        <v>-0.4287</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2144</v>
+        <v>0.134</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1953</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3446</v>
+        <v>-0.5138</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3349</v>
+        <v>-0.2537</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0097</v>
+        <v>-0.2601</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9414</v>
+        <v>-0.3869</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6642</v>
+        <v>-0.3869</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484291_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. PRAT PRUNA</t>
+          <t>M. TORNE DELAURENS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2572</v>
+        <v>-3.6388</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.042</v>
+        <v>-1.8721</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2152</v>
+        <v>-1.7667</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.2101</v>
+        <v>-2.5482</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.6035</v>
+        <v>-1.3339</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6066</v>
+        <v>-1.2144</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.2589</v>
+        <v>0.1036</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.3047</v>
+        <v>0.1036</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9542</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.0488</v>
+        <v>-2.6518</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2988</v>
+        <v>-1.4375</v>
       </c>
       <c r="O11" t="n">
-        <v>1.3476</v>
+        <v>-1.2144</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.7348</v>
+        <v>0.1953</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
         <v>1.1721</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0784</v>
+        <v>-0.3446</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0772</v>
+        <v>-0.3349</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0011</v>
+        <v>-0.0097</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6093</v>
+        <v>-0.9414</v>
       </c>
       <c r="W11" t="n">
-        <v>3.0466</v>
+        <v>-0.6642</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.4373</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484291_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>G. PRAT PRUNA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.2698</v>
+        <v>-4.2572</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.381</v>
+        <v>-4.042</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8887</v>
+        <v>-0.2152</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.7477</v>
+        <v>-2.2101</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5513</v>
+        <v>-1.6035</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.1964</v>
+        <v>-0.6066</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.956</v>
+        <v>-3.2589</v>
       </c>
       <c r="K12" t="n">
-        <v>1.0258</v>
+        <v>-1.3047</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.9818</v>
+        <v>-1.9542</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.7917</v>
+        <v>1.0488</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.5771</v>
+        <v>-0.2988</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.2146</v>
+        <v>1.3476</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1953</v>
+        <v>-2.7348</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3267</v>
+        <v>0.0784</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7255</v>
+        <v>0.0772</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3988</v>
+        <v>0.0011</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2772</v>
+        <v>3.0466</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2772</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484291_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. VINALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,151 +1483,157 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-16.1046</v>
+        <v>-4.5768</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.197000000000001</v>
+        <v>-2.688</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.907500000000001</v>
+        <v>-1.8887</v>
       </c>
       <c r="G13" t="n">
-        <v>-14.8828</v>
+        <v>-4.0547</v>
       </c>
       <c r="H13" t="n">
-        <v>-9.4861</v>
+        <v>-0.8583</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.396700000000001</v>
+        <v>-3.1964</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.148</v>
+        <v>-1.263</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.1307999999999998</v>
+        <v>0.7188</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.017300000000001</v>
+        <v>-1.9818</v>
       </c>
       <c r="M13" t="n">
-        <v>-12.7347</v>
+        <v>-2.7917</v>
       </c>
       <c r="N13" t="n">
-        <v>-9.3552</v>
+        <v>-1.5771</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.3795</v>
+        <v>-1.2146</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9765999999999995</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q13" t="n">
-        <v>-10.7438</v>
+        <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>9.7674</v>
+        <v>0.7814</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.627400000000001</v>
+        <v>-0.3267</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.897</v>
+        <v>-0.7255</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7304999999999999</v>
+        <v>0.3988</v>
       </c>
       <c r="V13" t="n">
-        <v>2.3825</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>7.592</v>
+        <v>0.2772</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.209499999999999</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484291_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. NDOYE</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+          <t>C.B. GRANOLLERS</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.848</v>
+        <v>-16.1046</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0013</v>
+        <v>-7.196999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>3.8466</v>
+        <v>-8.907500000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>3.6733</v>
+        <v>-14.8828</v>
       </c>
       <c r="H14" t="n">
-        <v>2.4331</v>
+        <v>-9.4861</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2402</v>
+        <v>-5.396699999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>2.949</v>
+        <v>-2.147999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7871</v>
+        <v>-0.1308</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1619</v>
+        <v>-2.017300000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7243000000000001</v>
+        <v>-12.7347</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.354</v>
+        <v>-9.3552</v>
       </c>
       <c r="O14" t="n">
-        <v>1.0784</v>
+        <v>-3.3795</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3907</v>
+        <v>-0.9765999999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1721</v>
+        <v>-10.7438</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5627</v>
+        <v>9.767399999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5105</v>
+        <v>-2.627400000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.615</v>
+        <v>-1.897</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8954</v>
+        <v>-0.7304999999999997</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2735</v>
+        <v>2.3825</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6093</v>
+        <v>7.592</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6642</v>
-      </c>
+        <v>-5.209499999999999</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. HERNANDEZ GIMENEZ</t>
+          <t>S. NDOYE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.9021</v>
+        <v>6.848</v>
       </c>
       <c r="E15" t="n">
-        <v>6.3608</v>
+        <v>3.0013</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4587</v>
+        <v>3.8466</v>
       </c>
       <c r="G15" t="n">
-        <v>5.1194</v>
+        <v>3.6733</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7302</v>
+        <v>2.4331</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3893</v>
+        <v>1.2402</v>
       </c>
       <c r="J15" t="n">
-        <v>5.6333</v>
+        <v>2.949</v>
       </c>
       <c r="K15" t="n">
-        <v>3.3781</v>
+        <v>2.7871</v>
       </c>
       <c r="L15" t="n">
-        <v>2.2552</v>
+        <v>0.1619</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5139</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.648</v>
+        <v>-0.354</v>
       </c>
       <c r="O15" t="n">
-        <v>0.134</v>
+        <v>1.0784</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.3441</v>
+        <v>-1.1721</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1488</v>
+        <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0915</v>
+        <v>1.5105</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2522</v>
+        <v>0.615</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3437</v>
+        <v>0.8954</v>
       </c>
       <c r="V15" t="n">
-        <v>0.8865</v>
+        <v>1.2735</v>
       </c>
       <c r="W15" t="n">
-        <v>3.3238</v>
+        <v>0.6093</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.4373</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484291_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. BAGUR PONS</t>
+          <t>J. HERNANDEZ GIMENEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4879</v>
+        <v>5.9021</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6451</v>
+        <v>6.3608</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8428</v>
+        <v>-0.4587</v>
       </c>
       <c r="G16" t="n">
-        <v>3.4876</v>
+        <v>5.1194</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3413</v>
+        <v>2.7302</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1463</v>
+        <v>2.3893</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5637</v>
+        <v>5.6333</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8215</v>
+        <v>3.3781</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7422</v>
+        <v>2.2552</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9239000000000001</v>
+        <v>-0.5139</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5199</v>
+        <v>-0.648</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4041</v>
+        <v>0.134</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7814</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.3441</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7814</v>
+        <v>2.1488</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4924</v>
+        <v>0.0915</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2544</v>
+        <v>-0.2522</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7468</v>
+        <v>0.3437</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2735</v>
+        <v>0.8865</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6642</v>
+        <v>3.3238</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6093</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484291_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. GOMEZ PRIVAT</t>
+          <t>P. BAGUR PONS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3926</v>
+        <v>3.4879</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0044</v>
+        <v>1.6451</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3882</v>
+        <v>1.8428</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0669</v>
+        <v>3.4876</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8755</v>
+        <v>2.3413</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8085</v>
+        <v>1.1463</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3527</v>
+        <v>2.5637</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6999</v>
+        <v>1.8215</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.3472</v>
+        <v>0.7422</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7141999999999999</v>
+        <v>0.9239000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1755</v>
+        <v>0.5199</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5387</v>
+        <v>0.4041</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5627</v>
+        <v>0.7814</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2588</v>
+        <v>0.4924</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7651</v>
+        <v>-0.2544</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4937</v>
+        <v>0.7468</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.1052</v>
+        <v>-1.2735</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2772</v>
+        <v>-0.6642</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.3824</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484291_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. TALTAVULL BALLE</t>
+          <t>R. GOMEZ PRIVAT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1297</v>
+        <v>1.3926</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5739</v>
+        <v>1.0044</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5558</v>
+        <v>0.3882</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9041</v>
+        <v>1.0669</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7693</v>
+        <v>1.8755</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1348</v>
+        <v>-0.8085</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6344</v>
+        <v>0.3527</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6344</v>
+        <v>1.6999</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-1.3472</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2696</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1348</v>
+        <v>0.1755</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1348</v>
+        <v>0.5387</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.3907</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0303</v>
+        <v>1.2588</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0605</v>
+        <v>0.7651</v>
       </c>
       <c r="U18" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.4937</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-2.1052</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.3824</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484291_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. CORBERA BUSQUETA</t>
+          <t>P. TALTAVULL BALLE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6407</v>
+        <v>1.1297</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8573</v>
+        <v>0.5739</v>
       </c>
       <c r="F19" t="n">
-        <v>2.498</v>
+        <v>0.5558</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5958</v>
+        <v>0.9041</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1108</v>
+        <v>0.7693</v>
       </c>
       <c r="I19" t="n">
-        <v>0.485</v>
+        <v>0.1348</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0436</v>
+        <v>0.6344</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2597</v>
+        <v>0.6344</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2161</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6393</v>
+        <v>0.2696</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3705</v>
+        <v>0.1348</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2688</v>
+        <v>0.1348</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.1488</v>
+        <v>0.1953</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.3208</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0337</v>
+        <v>0.0303</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.266</v>
+        <v>-0.0605</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2997</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.7731</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3869</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484291_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. LLUFRIU ARCOS</t>
+          <t>M. CORBERA BUSQUETA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4306</v>
+        <v>0.6407</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6848</v>
+        <v>-1.8573</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2542</v>
+        <v>2.498</v>
       </c>
       <c r="G20" t="n">
-        <v>2.1043</v>
+        <v>0.5958</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0243</v>
+        <v>0.1108</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0799</v>
+        <v>0.485</v>
       </c>
       <c r="J20" t="n">
-        <v>2.5338</v>
+        <v>-0.0436</v>
       </c>
       <c r="K20" t="n">
-        <v>0.779</v>
+        <v>-0.2597</v>
       </c>
       <c r="L20" t="n">
-        <v>1.7548</v>
+        <v>0.2161</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4295</v>
+        <v>0.6393</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2454</v>
+        <v>0.3705</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6749000000000001</v>
+        <v>0.2688</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3907</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.1953</v>
+        <v>-3.3208</v>
       </c>
       <c r="R20" t="n">
-        <v>0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1816</v>
+        <v>0.0337</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2667</v>
+        <v>-0.266</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0851</v>
+        <v>0.2997</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.8828</v>
+        <v>2.16</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3869</v>
+        <v>1.7731</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.4959</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484291_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. ANDUJAR MASCARO</t>
+          <t>S. LLUFRIU ARCOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.023</v>
+        <v>0.4306</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4732</v>
+        <v>1.6848</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4962</v>
+        <v>-1.2542</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0172</v>
+        <v>2.1043</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0691</v>
+        <v>1.0243</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0519</v>
+        <v>1.0799</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2723</v>
+        <v>2.5338</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5104</v>
+        <v>0.779</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7827</v>
+        <v>1.7548</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2895</v>
+        <v>-0.4295</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5587</v>
+        <v>0.2454</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2692</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P21" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="R21" t="n">
         <v>0.586</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-0.9767</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.5627</v>
-      </c>
       <c r="S21" t="n">
-        <v>0.6727</v>
+        <v>-0.1816</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2312</v>
+        <v>-0.2667</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4415</v>
+        <v>0.0851</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2186</v>
+        <v>-1.8828</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.3869</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2186</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484291_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>L. ANDUJAR MASCARO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4251</v>
+        <v>0.023</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0323</v>
+        <v>-0.4732</v>
       </c>
       <c r="F22" t="n">
-        <v>1.6072</v>
+        <v>0.4962</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.0515</v>
+        <v>-0.0172</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7294</v>
+        <v>-1.0691</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.3221</v>
+        <v>1.0519</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.1611</v>
+        <v>0.2723</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9747</v>
+        <v>-0.5104</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.1863</v>
+        <v>0.7827</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1096</v>
+        <v>-0.2895</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2454</v>
+        <v>-0.5587</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1358</v>
+        <v>0.2692</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.3674</v>
+        <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S22" t="n">
-        <v>1.0441</v>
+        <v>0.6727</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2189</v>
+        <v>0.2312</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8252</v>
+        <v>0.4415</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2224</v>
+        <v>-1.2186</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.4996</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484291_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>G. GARCIA RIERA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,68 +2309,152 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
+        <v>-1.4251</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-3.0323</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.6072</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-2.0515</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.7294</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-1.3221</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-2.1611</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-0.9747</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-1.1863</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.1096</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.2454</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.1358</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-1.3674</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.0441</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.2189</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.8252</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-0.2224</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-0.4996</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484291_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
         <v>18.4295</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E24" t="n">
         <v>8.907499999999999</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F24" t="n">
         <v>9.5219</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G24" t="n">
         <v>14.8827</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H24" t="n">
         <v>9.485999999999999</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I24" t="n">
         <v>5.396800000000001</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J24" t="n">
         <v>12.7345</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K24" t="n">
         <v>9.3552</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L24" t="n">
         <v>3.3794</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M24" t="n">
         <v>2.148</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N24" t="n">
         <v>0.1308</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O24" t="n">
         <v>2.0173</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P24" t="n">
         <v>0.9767999999999997</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q24" t="n">
         <v>-9.767099999999999</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R24" t="n">
         <v>10.7438</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S24" t="n">
         <v>4.9524</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T24" t="n">
         <v>0.7303999999999999</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U24" t="n">
         <v>4.2219</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V24" t="n">
         <v>-2.3825</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W24" t="n">
         <v>5.209499999999999</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X24" t="n">
         <v>-7.592</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
